--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56F4593D-DBCB-42AD-82DD-F78177B6CD08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3873104-5FE3-4204-8429-7DA41A2FC00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="297">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -932,6 +932,9 @@
   </si>
   <si>
     <t>Losses</t>
+  </si>
+  <si>
+    <t>OT</t>
   </si>
 </sst>
 </file>
@@ -1089,12 +1092,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="46" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1316,14 +1319,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="3" spans="1:6" ht="30">
       <c r="A3" s="1" t="s">
@@ -1424,15 +1427,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
       <c r="H1" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="15">
@@ -3674,15 +3677,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
     </row>
     <row r="3" spans="1:7" ht="30">
       <c r="A3" s="6" t="s">
@@ -4296,25 +4299,25 @@
       <c r="G31" s="18"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="19">
         <v>81</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="F32" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="G32" s="20"/>
+      <c r="G32" s="19"/>
       <c r="H32" s="13"/>
     </row>
     <row r="33" spans="1:8">
@@ -5879,21 +5882,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
     </row>
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
@@ -5994,13 +5997,18 @@
       <c r="F5" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J5" s="7"/>
+      <c r="G5" s="7">
+        <v>5</v>
+      </c>
+      <c r="H5" s="7">
+        <v>4</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>296</v>
+      </c>
       <c r="K5" s="7" t="s">
         <v>46</v>
       </c>
@@ -9934,18 +9942,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="6" t="s">
@@ -10060,7 +10068,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="10">
-        <f t="shared" ref="G5:G67" si="0">IF(AND(E6="",F6=""),"",SUM(E6:F6))</f>
+        <f t="shared" ref="G6:G67" si="0">IF(AND(E6="",F6=""),"",SUM(E6:F6))</f>
         <v>1</v>
       </c>
       <c r="H6" s="7">
@@ -19023,19 +19031,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="6" t="s">
@@ -19083,7 +19091,7 @@
         <f>IF(B4="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v>Aaron Burton</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>1.6666666666666667</v>
       </c>
       <c r="E4" s="7">
@@ -23467,18 +23475,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
@@ -23945,18 +23953,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>283</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
@@ -24210,18 +24218,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
@@ -24318,7 +24326,7 @@
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24368,7 +24376,7 @@
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24418,7 +24426,7 @@
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25421,43 +25429,43 @@
       <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="21" t="str">
+      <c r="A30" s="20" t="str">
         <f>IF(Players!A30="","",Players!A30)</f>
         <v>P027</v>
       </c>
-      <c r="B30" s="21" t="str">
+      <c r="B30" s="20" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Charles Coney</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="20">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>88</v>
       </c>
-      <c r="D30" s="21" t="str">
+      <c r="D30" s="20" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="20">
         <f>IF(A30="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A30,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="20">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="21">
+      <c r="G30" s="20">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="21">
+      <c r="H30" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="21">
+      <c r="I30" s="20">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="J30" s="21">
+      <c r="J30" s="20">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3873104-5FE3-4204-8429-7DA41A2FC00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4800" yWindow="4725" windowWidth="21600" windowHeight="11295" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -23525,7 +23525,7 @@
         <v>107</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -23537,13 +23537,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -23557,10 +23557,10 @@
         <v>86</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -23572,16 +23572,16 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -23589,7 +23589,7 @@
         <v>75</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -23598,22 +23598,22 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -23621,7 +23621,7 @@
         <v>48</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -23633,13 +23633,13 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -23653,7 +23653,7 @@
         <v>59</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -23665,13 +23665,13 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -23685,10 +23685,10 @@
         <v>69</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -23700,16 +23700,16 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -23717,10 +23717,10 @@
         <v>53</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -23732,13 +23732,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -23749,7 +23749,7 @@
         <v>102</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -23761,13 +23761,13 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -23781,10 +23781,10 @@
         <v>31</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -23796,7 +23796,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -23805,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -23813,13 +23813,13 @@
         <v>81</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -23828,16 +23828,16 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -23845,7 +23845,7 @@
         <v>64</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -23857,13 +23857,13 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -23877,10 +23877,10 @@
         <v>91</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -23892,16 +23892,16 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -23909,7 +23909,7 @@
         <v>96</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -23921,13 +23921,13 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>0</v>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MWard1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2E96A83-2E91-43CF-A888-A6968E5C460E}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="4725" windowWidth="21600" windowHeight="11295" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -23546,7 +23546,7 @@
         <v>32</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -23578,7 +23578,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -23610,7 +23610,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -23642,7 +23642,7 @@
         <v>12</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -23674,7 +23674,7 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -23706,7 +23706,7 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>3</v>
@@ -23738,7 +23738,7 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -23770,7 +23770,7 @@
         <v>17</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -23834,7 +23834,7 @@
         <v>2</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -23866,7 +23866,7 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -23898,7 +23898,7 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J15">
         <v>9</v>
@@ -23930,7 +23930,7 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
         <v>0</v>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2E96A83-2E91-43CF-A888-A6968E5C460E}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CA9C725-6A10-456F-833B-44D36244B419}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -6036,11 +6036,15 @@
       <c r="F6" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+      <c r="G6" s="7">
+        <v>5</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
       <c r="I6" s="10" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>W</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
@@ -24326,7 +24330,7 @@
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24426,7 +24430,7 @@
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CA9C725-6A10-456F-833B-44D36244B419}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45860A39-1A1F-49CE-9FA6-B2A28B09A721}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="5385" windowWidth="21600" windowHeight="11295" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -24007,10 +24007,10 @@
         <v>86</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -24022,16 +24022,16 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -24039,7 +24039,7 @@
         <v>48</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -24051,13 +24051,13 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -24071,10 +24071,10 @@
         <v>53</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -24086,16 +24086,16 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -24103,7 +24103,7 @@
         <v>102</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -24115,13 +24115,13 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -24135,10 +24135,10 @@
         <v>31</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -24150,7 +24150,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -24159,7 +24159,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -24167,7 +24167,7 @@
         <v>96</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -24179,13 +24179,13 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>0</v>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45860A39-1A1F-49CE-9FA6-B2A28B09A721}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8449F42-B270-4121-A92F-291BE27629BF}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5385" windowWidth="21600" windowHeight="11295" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="298">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -935,6 +935,9 @@
   </si>
   <si>
     <t>OT</t>
+  </si>
+  <si>
+    <t>SO</t>
   </si>
 </sst>
 </file>
@@ -6074,10 +6077,18 @@
       <c r="F7" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="7"/>
+      <c r="G7" s="7">
+        <v>4</v>
+      </c>
+      <c r="H7" s="7">
+        <v>5</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>296</v>
+      </c>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
@@ -6105,13 +6116,19 @@
       <c r="F8" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="G8" s="7">
+        <v>6</v>
+      </c>
+      <c r="H8" s="7">
+        <v>7</v>
+      </c>
       <c r="I8" s="10" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="7"/>
+        <v>L</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>297</v>
+      </c>
       <c r="K8" s="7" t="s">
         <v>230</v>
       </c>
@@ -24330,7 +24347,7 @@
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24380,7 +24397,7 @@
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24480,7 +24497,7 @@
       </c>
       <c r="M7" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8449F42-B270-4121-A92F-291BE27629BF}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B73F2D8-F3C2-4DB2-8A20-F56C01066621}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2925" yWindow="1890" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -6087,7 +6087,7 @@
         <v>278</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>56</v>
@@ -6127,7 +6127,7 @@
         <v>L</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>230</v>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B73F2D8-F3C2-4DB2-8A20-F56C01066621}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{389B5BCB-6C44-4480-8857-41DF399C5FB5}"/>
   <bookViews>
-    <workbookView xWindow="2925" yWindow="1890" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="298">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -5880,7 +5880,7 @@
     <col min="9" max="9" width="6.75" customWidth="1"/>
     <col min="10" max="10" width="6.25" customWidth="1"/>
     <col min="11" max="11" width="35.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.625" customWidth="1"/>
+    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5976,9 +5976,7 @@
       <c r="K4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>225</v>
-      </c>
+      <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:13">
@@ -6015,9 +6013,7 @@
       <c r="K5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="7" t="s">
-        <v>225</v>
-      </c>
+      <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:13">
@@ -6053,9 +6049,7 @@
       <c r="K6" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>225</v>
-      </c>
+      <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:13">
@@ -6092,9 +6086,7 @@
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>225</v>
-      </c>
+      <c r="L7" s="7"/>
       <c r="M7" s="7"/>
     </row>
     <row r="8" spans="1:13">
@@ -6132,9 +6124,7 @@
       <c r="K8" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>225</v>
-      </c>
+      <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:13">
@@ -6176,13 +6166,13 @@
         <v>235</v>
       </c>
       <c r="B10" s="8">
-        <v>46298</v>
+        <v>46292</v>
       </c>
       <c r="C10" s="9">
         <v>0.77083333333333337</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>228</v>
@@ -6192,10 +6182,7 @@
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
-      <c r="I10" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="I10" s="10"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7" t="s">
         <v>230</v>
@@ -6210,19 +6197,19 @@
         <v>236</v>
       </c>
       <c r="B11" s="8">
-        <v>46306</v>
+        <v>46298</v>
       </c>
       <c r="C11" s="9">
-        <v>0.83333333333333304</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>228</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
@@ -6244,19 +6231,19 @@
         <v>237</v>
       </c>
       <c r="B12" s="8">
-        <v>46312</v>
+        <v>46306</v>
       </c>
       <c r="C12" s="9">
-        <v>0.72916666666666663</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -6266,7 +6253,7 @@
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7" t="s">
-        <v>105</v>
+        <v>230</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>225</v>
@@ -6278,16 +6265,16 @@
         <v>238</v>
       </c>
       <c r="B13" s="8">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="C13" s="9">
-        <v>0.77083333333333304</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>229</v>
@@ -6300,7 +6287,7 @@
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7" t="s">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>225</v>
@@ -6312,16 +6299,16 @@
         <v>239</v>
       </c>
       <c r="B14" s="8">
-        <v>46327</v>
+        <v>46320</v>
       </c>
       <c r="C14" s="9">
-        <v>0.75</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>229</v>
@@ -6334,7 +6321,7 @@
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>51</v>
+        <v>230</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>225</v>
@@ -6346,16 +6333,16 @@
         <v>240</v>
       </c>
       <c r="B15" s="8">
-        <v>46334</v>
+        <v>46327</v>
       </c>
       <c r="C15" s="9">
         <v>0.75</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>229</v>
@@ -6368,7 +6355,7 @@
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>230</v>
+        <v>51</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>225</v>
@@ -6380,19 +6367,19 @@
         <v>241</v>
       </c>
       <c r="B16" s="8">
-        <v>46340</v>
+        <v>46334</v>
       </c>
       <c r="C16" s="9">
-        <v>0.79166666666666696</v>
+        <v>0.75</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>228</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -6414,19 +6401,19 @@
         <v>242</v>
       </c>
       <c r="B17" s="8">
-        <v>46341</v>
+        <v>46340</v>
       </c>
       <c r="C17" s="9">
-        <v>0.70833333333333337</v>
+        <v>0.79166666666666696</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -6436,7 +6423,7 @@
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7" t="s">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>225</v>
@@ -6448,13 +6435,13 @@
         <v>243</v>
       </c>
       <c r="B18" s="8">
-        <v>46354</v>
+        <v>46341</v>
       </c>
       <c r="C18" s="9">
-        <v>0.79166666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>223</v>
@@ -6470,7 +6457,7 @@
       </c>
       <c r="J18" s="7"/>
       <c r="K18" s="7" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>225</v>
@@ -6482,19 +6469,19 @@
         <v>244</v>
       </c>
       <c r="B19" s="8">
-        <v>46355</v>
+        <v>46354</v>
       </c>
       <c r="C19" s="9">
-        <v>0.72916666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>223</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -6504,7 +6491,7 @@
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>225</v>
@@ -6516,13 +6503,13 @@
         <v>245</v>
       </c>
       <c r="B20" s="8">
-        <v>46368</v>
+        <v>46355</v>
       </c>
       <c r="C20" s="9">
-        <v>0.8125</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>223</v>
@@ -6538,7 +6525,7 @@
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>225</v>
@@ -6550,16 +6537,16 @@
         <v>246</v>
       </c>
       <c r="B21" s="8">
-        <v>46369</v>
+        <v>46368</v>
       </c>
       <c r="C21" s="9">
-        <v>0.77083333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>233</v>
@@ -6572,7 +6559,7 @@
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7" t="s">
-        <v>230</v>
+        <v>67</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>225</v>
@@ -6584,19 +6571,19 @@
         <v>247</v>
       </c>
       <c r="B22" s="8">
-        <v>46376</v>
+        <v>46369</v>
       </c>
       <c r="C22" s="9">
         <v>0.77083333333333337</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>228</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -19015,17 +19002,17 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000001000000}">
+          <x14:formula1>
+            <xm:f>Players!$A$4:$A$200</xm:f>
+          </x14:formula1>
+          <xm:sqref>B4:B500</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000000000000}">
           <x14:formula1>
             <xm:f>Games!$A$4:$A$200</xm:f>
           </x14:formula1>
           <xm:sqref>A4:A500</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000001000000}">
-          <x14:formula1>
-            <xm:f>Players!$A$4:$A$200</xm:f>
-          </x14:formula1>
-          <xm:sqref>B4:B500</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -23469,17 +23456,17 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0400-000001000000}">
+          <x14:formula1>
+            <xm:f>Players!$A$4:$A$200</xm:f>
+          </x14:formula1>
+          <xm:sqref>B4:B200</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0400-000000000000}">
           <x14:formula1>
             <xm:f>Games!$A$4:$A$200</xm:f>
           </x14:formula1>
           <xm:sqref>A4:A200</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0400-000001000000}">
-          <x14:formula1>
-            <xm:f>Players!$A$4:$A$200</xm:f>
-          </x14:formula1>
-          <xm:sqref>B4:B200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{389B5BCB-6C44-4480-8857-41DF399C5FB5}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DA8B0FC-EBCA-4D2D-BDAB-6DFFD216DC29}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6172,7 +6172,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>228</v>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DA8B0FC-EBCA-4D2D-BDAB-6DFFD216DC29}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{305501F6-CFF9-48A3-9AB8-B30FA8A27F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="298">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -721,42 +721,54 @@
     <t>Pre-season</t>
   </si>
   <si>
+    <t>G002</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>OT</t>
+  </si>
+  <si>
+    <t>G003</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>League/Cup</t>
+  </si>
+  <si>
+    <t>Planet Ice Milton Keynes</t>
+  </si>
+  <si>
+    <t>G004</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>SO</t>
+  </si>
+  <si>
+    <t>G005</t>
+  </si>
+  <si>
+    <t>League</t>
+  </si>
+  <si>
+    <t>G006</t>
+  </si>
+  <si>
+    <t>G007</t>
+  </si>
+  <si>
+    <t>G008</t>
+  </si>
+  <si>
     <t>Upcoming</t>
   </si>
   <si>
-    <t>G002</t>
-  </si>
-  <si>
-    <t>G003</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>League/Cup</t>
-  </si>
-  <si>
-    <t>Planet Ice Milton Keynes</t>
-  </si>
-  <si>
-    <t>G004</t>
-  </si>
-  <si>
-    <t>G005</t>
-  </si>
-  <si>
-    <t>League</t>
-  </si>
-  <si>
-    <t>G006</t>
-  </si>
-  <si>
-    <t>G007</t>
-  </si>
-  <si>
-    <t>G008</t>
-  </si>
-  <si>
     <t>G009</t>
   </si>
   <si>
@@ -871,18 +883,12 @@
     <t>GP</t>
   </si>
   <si>
-    <t>W</t>
-  </si>
-  <si>
     <t>OTW</t>
   </si>
   <si>
     <t>OTL</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>GF</t>
   </si>
   <si>
@@ -932,12 +938,6 @@
   </si>
   <si>
     <t>Losses</t>
-  </si>
-  <si>
-    <t>OT</t>
-  </si>
-  <si>
-    <t>SO</t>
   </si>
 </sst>
 </file>
@@ -5981,7 +5981,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B5" s="8">
         <v>46270</v>
@@ -6005,10 +6005,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>296</v>
+        <v>227</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>46</v>
@@ -6018,7 +6018,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B6" s="8">
         <v>46278</v>
@@ -6030,10 +6030,10 @@
         <v>47</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
@@ -6047,14 +6047,14 @@
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B7" s="8">
         <v>46284</v>
@@ -6069,7 +6069,7 @@
         <v>223</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G7" s="7">
         <v>4</v>
@@ -6078,10 +6078,10 @@
         <v>5</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>297</v>
+        <v>234</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>56</v>
@@ -6091,7 +6091,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="7" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B8" s="8">
         <v>46285</v>
@@ -6103,10 +6103,10 @@
         <v>58</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G8" s="7">
         <v>6</v>
@@ -6119,17 +6119,17 @@
         <v>L</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>296</v>
+        <v>227</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B9" s="8">
         <v>46291</v>
@@ -6144,26 +6144,28 @@
         <v>223</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+        <v>236</v>
+      </c>
+      <c r="G9" s="7">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7">
+        <v>2</v>
+      </c>
       <c r="I9" s="10" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>L</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="L9" s="7" t="s">
-        <v>225</v>
-      </c>
+      <c r="L9" s="7"/>
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B10" s="8">
         <v>46292</v>
@@ -6175,26 +6177,30 @@
         <v>85</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="10"/>
+        <v>230</v>
+      </c>
+      <c r="G10" s="7">
+        <v>5</v>
+      </c>
+      <c r="H10" s="7">
+        <v>3</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>226</v>
+      </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>225</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="7" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B11" s="8">
         <v>46298</v>
@@ -6206,10 +6212,10 @@
         <v>101</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
@@ -6219,16 +6225,16 @@
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B12" s="8">
         <v>46306</v>
@@ -6240,10 +6246,10 @@
         <v>106</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -6253,16 +6259,16 @@
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="7" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B13" s="8">
         <v>46312</v>
@@ -6277,7 +6283,7 @@
         <v>223</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -6290,13 +6296,13 @@
         <v>105</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="7" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B14" s="8">
         <v>46320</v>
@@ -6308,10 +6314,10 @@
         <v>95</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -6321,16 +6327,16 @@
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="7" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B15" s="8">
         <v>46327</v>
@@ -6345,7 +6351,7 @@
         <v>223</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -6358,13 +6364,13 @@
         <v>51</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="7" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B16" s="8">
         <v>46334</v>
@@ -6376,10 +6382,10 @@
         <v>52</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -6389,16 +6395,16 @@
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B17" s="8">
         <v>46340</v>
@@ -6410,10 +6416,10 @@
         <v>74</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -6423,16 +6429,16 @@
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M17" s="7"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="7" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B18" s="8">
         <v>46341</v>
@@ -6447,7 +6453,7 @@
         <v>223</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -6460,13 +6466,13 @@
         <v>99</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M18" s="7"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B19" s="8">
         <v>46354</v>
@@ -6481,7 +6487,7 @@
         <v>223</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -6494,13 +6500,13 @@
         <v>89</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M19" s="7"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B20" s="8">
         <v>46355</v>
@@ -6515,7 +6521,7 @@
         <v>223</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -6528,13 +6534,13 @@
         <v>62</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B21" s="8">
         <v>46368</v>
@@ -6549,7 +6555,7 @@
         <v>223</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -6562,13 +6568,13 @@
         <v>67</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M21" s="7"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="7" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B22" s="8">
         <v>46369</v>
@@ -6580,10 +6586,10 @@
         <v>68</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -6593,16 +6599,16 @@
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M22" s="7"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B23" s="8">
         <v>46397</v>
@@ -6614,10 +6620,10 @@
         <v>80</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -6627,16 +6633,16 @@
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B24" s="8">
         <v>46417</v>
@@ -6648,10 +6654,10 @@
         <v>90</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -6661,16 +6667,16 @@
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B25" s="8">
         <v>46425</v>
@@ -6682,10 +6688,10 @@
         <v>63</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -6695,16 +6701,16 @@
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M25" s="7"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="7" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B26" s="8">
         <v>46446</v>
@@ -6719,7 +6725,7 @@
         <v>223</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -6732,13 +6738,13 @@
         <v>84</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M26" s="7"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="7" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B27" s="8">
         <v>46452</v>
@@ -6753,7 +6759,7 @@
         <v>223</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -6766,13 +6772,13 @@
         <v>72</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M27" s="7"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B28" s="8">
         <v>46459</v>
@@ -6787,7 +6793,7 @@
         <v>223</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -6800,13 +6806,13 @@
         <v>110</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M28" s="7"/>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="7" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B29" s="8">
         <v>46467</v>
@@ -6821,7 +6827,7 @@
         <v>223</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
@@ -6834,7 +6840,7 @@
         <v>94</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M29" s="7"/>
     </row>
@@ -9951,7 +9957,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -9971,25 +9977,25 @@
         <v>111</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>116</v>
@@ -10007,7 +10013,7 @@
         <v>Sam Peters</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E4" s="7">
         <v>0</v>
@@ -19040,7 +19046,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -19064,25 +19070,25 @@
         <v>131</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>116</v>
@@ -23484,7 +23490,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -23498,34 +23504,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23962,7 +23968,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -23976,34 +23982,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -24227,7 +24233,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -24241,10 +24247,10 @@
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -24252,35 +24258,35 @@
         <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>223</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K3" s="13"/>
       <c r="L3" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M3" s="12">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -24330,11 +24336,11 @@
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24380,11 +24386,11 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24430,11 +24436,11 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24480,11 +24486,11 @@
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M7" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{305501F6-CFF9-48A3-9AB8-B30FA8A27F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="223" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2347A85-3F4B-47A6-A22E-C04992FEF68B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5685" yWindow="3525" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="298">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -721,223 +721,223 @@
     <t>Pre-season</t>
   </si>
   <si>
+    <t>Upcoming</t>
+  </si>
+  <si>
     <t>G002</t>
   </si>
   <si>
+    <t>G003</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>League/Cup</t>
+  </si>
+  <si>
+    <t>Planet Ice Milton Keynes</t>
+  </si>
+  <si>
+    <t>G004</t>
+  </si>
+  <si>
+    <t>G005</t>
+  </si>
+  <si>
+    <t>League</t>
+  </si>
+  <si>
+    <t>G006</t>
+  </si>
+  <si>
+    <t>G007</t>
+  </si>
+  <si>
+    <t>G008</t>
+  </si>
+  <si>
+    <t>G009</t>
+  </si>
+  <si>
+    <t>G010</t>
+  </si>
+  <si>
+    <t>G011</t>
+  </si>
+  <si>
+    <t>G012</t>
+  </si>
+  <si>
+    <t>G013</t>
+  </si>
+  <si>
+    <t>G014</t>
+  </si>
+  <si>
+    <t>G015</t>
+  </si>
+  <si>
+    <t>G016</t>
+  </si>
+  <si>
+    <t>G017</t>
+  </si>
+  <si>
+    <t>G018</t>
+  </si>
+  <si>
+    <t>G019</t>
+  </si>
+  <si>
+    <t>G020</t>
+  </si>
+  <si>
+    <t>G021</t>
+  </si>
+  <si>
+    <t>G022</t>
+  </si>
+  <si>
+    <t>G023</t>
+  </si>
+  <si>
+    <t>G024</t>
+  </si>
+  <si>
+    <t>G025</t>
+  </si>
+  <si>
+    <t>G026</t>
+  </si>
+  <si>
+    <t>Player Game Stats – one row per player per game</t>
+  </si>
+  <si>
+    <t>Player Name</t>
+  </si>
+  <si>
+    <t>Dressed?</t>
+  </si>
+  <si>
+    <t>Goals</t>
+  </si>
+  <si>
+    <t>Assists</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>PIM</t>
+  </si>
+  <si>
+    <t>+/-</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Netminder Game Stats</t>
+  </si>
+  <si>
+    <t>Minutes</t>
+  </si>
+  <si>
+    <t>Shots Against</t>
+  </si>
+  <si>
+    <t>Goals Against</t>
+  </si>
+  <si>
+    <t>Saves</t>
+  </si>
+  <si>
+    <t>Save %</t>
+  </si>
+  <si>
+    <t>Shutout?</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>League Table</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>GP</t>
+  </si>
+  <si>
     <t>W</t>
   </si>
   <si>
+    <t>OTW</t>
+  </si>
+  <si>
+    <t>OTL</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>GF</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>Cup Table</t>
+  </si>
+  <si>
+    <t>MK Thunder Season Player Totals</t>
+  </si>
+  <si>
+    <t>Team KPIs</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Pos</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Games entered</t>
+  </si>
+  <si>
+    <t>Goals scored</t>
+  </si>
+  <si>
+    <t>Goals against</t>
+  </si>
+  <si>
+    <t>Wins</t>
+  </si>
+  <si>
+    <t>Losses</t>
+  </si>
+  <si>
     <t>OT</t>
   </si>
   <si>
-    <t>G003</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>League/Cup</t>
-  </si>
-  <si>
-    <t>Planet Ice Milton Keynes</t>
-  </si>
-  <si>
-    <t>G004</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>SO</t>
-  </si>
-  <si>
-    <t>G005</t>
-  </si>
-  <si>
-    <t>League</t>
-  </si>
-  <si>
-    <t>G006</t>
-  </si>
-  <si>
-    <t>G007</t>
-  </si>
-  <si>
-    <t>G008</t>
-  </si>
-  <si>
-    <t>Upcoming</t>
-  </si>
-  <si>
-    <t>G009</t>
-  </si>
-  <si>
-    <t>G010</t>
-  </si>
-  <si>
-    <t>G011</t>
-  </si>
-  <si>
-    <t>G012</t>
-  </si>
-  <si>
-    <t>G013</t>
-  </si>
-  <si>
-    <t>G014</t>
-  </si>
-  <si>
-    <t>G015</t>
-  </si>
-  <si>
-    <t>G016</t>
-  </si>
-  <si>
-    <t>G017</t>
-  </si>
-  <si>
-    <t>G018</t>
-  </si>
-  <si>
-    <t>G019</t>
-  </si>
-  <si>
-    <t>G020</t>
-  </si>
-  <si>
-    <t>G021</t>
-  </si>
-  <si>
-    <t>G022</t>
-  </si>
-  <si>
-    <t>G023</t>
-  </si>
-  <si>
-    <t>G024</t>
-  </si>
-  <si>
-    <t>G025</t>
-  </si>
-  <si>
-    <t>G026</t>
-  </si>
-  <si>
-    <t>Player Game Stats – one row per player per game</t>
-  </si>
-  <si>
-    <t>Player Name</t>
-  </si>
-  <si>
-    <t>Dressed?</t>
-  </si>
-  <si>
-    <t>Goals</t>
-  </si>
-  <si>
-    <t>Assists</t>
-  </si>
-  <si>
-    <t>Points</t>
-  </si>
-  <si>
-    <t>PIM</t>
-  </si>
-  <si>
-    <t>+/-</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Netminder Game Stats</t>
-  </si>
-  <si>
-    <t>Minutes</t>
-  </si>
-  <si>
-    <t>Shots Against</t>
-  </si>
-  <si>
-    <t>Goals Against</t>
-  </si>
-  <si>
-    <t>Saves</t>
-  </si>
-  <si>
-    <t>Save %</t>
-  </si>
-  <si>
-    <t>Shutout?</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>League Table</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>OTW</t>
-  </si>
-  <si>
-    <t>OTL</t>
-  </si>
-  <si>
-    <t>GF</t>
-  </si>
-  <si>
-    <t>GA</t>
-  </si>
-  <si>
-    <t>GD</t>
-  </si>
-  <si>
-    <t>PTS</t>
-  </si>
-  <si>
-    <t>Cup Table</t>
-  </si>
-  <si>
-    <t>MK Thunder Season Player Totals</t>
-  </si>
-  <si>
-    <t>Team KPIs</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Pos</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>Games entered</t>
-  </si>
-  <si>
-    <t>Goals scored</t>
-  </si>
-  <si>
-    <t>Goals against</t>
-  </si>
-  <si>
-    <t>Wins</t>
-  </si>
-  <si>
-    <t>Losses</t>
   </si>
 </sst>
 </file>
@@ -5981,7 +5981,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B5" s="8">
         <v>46270</v>
@@ -6005,10 +6005,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>46</v>
@@ -6018,7 +6018,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B6" s="8">
         <v>46278</v>
@@ -6030,10 +6030,10 @@
         <v>47</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>229</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>230</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
@@ -6047,14 +6047,14 @@
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B7" s="8">
         <v>46284</v>
@@ -6069,7 +6069,7 @@
         <v>223</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G7" s="7">
         <v>4</v>
@@ -6078,10 +6078,10 @@
         <v>5</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>234</v>
+        <v>297</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>56</v>
@@ -6091,7 +6091,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B8" s="8">
         <v>46285</v>
@@ -6103,10 +6103,10 @@
         <v>58</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G8" s="7">
         <v>6</v>
@@ -6119,17 +6119,17 @@
         <v>L</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B9" s="8">
         <v>46291</v>
@@ -6144,7 +6144,7 @@
         <v>223</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G9" s="7">
         <v>1</v>
@@ -6165,7 +6165,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B10" s="8">
         <v>46292</v>
@@ -6177,10 +6177,10 @@
         <v>85</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>229</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>230</v>
       </c>
       <c r="G10" s="7">
         <v>5</v>
@@ -6189,18 +6189,18 @@
         <v>3</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B11" s="8">
         <v>46298</v>
@@ -6212,29 +6212,31 @@
         <v>101</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="G11" s="7">
+        <v>4</v>
+      </c>
+      <c r="H11" s="7">
+        <v>1</v>
+      </c>
       <c r="I11" s="10" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>W</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>240</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="L11" s="7"/>
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="7" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B12" s="8">
         <v>46306</v>
@@ -6246,10 +6248,10 @@
         <v>106</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -6259,16 +6261,16 @@
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B13" s="8">
         <v>46312</v>
@@ -6283,7 +6285,7 @@
         <v>223</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -6296,13 +6298,13 @@
         <v>105</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="7" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B14" s="8">
         <v>46320</v>
@@ -6314,10 +6316,10 @@
         <v>95</v>
       </c>
       <c r="E14" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>229</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>230</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -6327,16 +6329,16 @@
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B15" s="8">
         <v>46327</v>
@@ -6351,7 +6353,7 @@
         <v>223</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -6364,13 +6366,13 @@
         <v>51</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="7" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B16" s="8">
         <v>46334</v>
@@ -6382,10 +6384,10 @@
         <v>52</v>
       </c>
       <c r="E16" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>229</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>230</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -6395,16 +6397,16 @@
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="7" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B17" s="8">
         <v>46340</v>
@@ -6416,10 +6418,10 @@
         <v>74</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -6429,16 +6431,16 @@
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M17" s="7"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="7" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B18" s="8">
         <v>46341</v>
@@ -6453,7 +6455,7 @@
         <v>223</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -6466,13 +6468,13 @@
         <v>99</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M18" s="7"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="7" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B19" s="8">
         <v>46354</v>
@@ -6487,7 +6489,7 @@
         <v>223</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -6500,13 +6502,13 @@
         <v>89</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M19" s="7"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="7" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B20" s="8">
         <v>46355</v>
@@ -6521,7 +6523,7 @@
         <v>223</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -6534,13 +6536,13 @@
         <v>62</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="7" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B21" s="8">
         <v>46368</v>
@@ -6555,7 +6557,7 @@
         <v>223</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -6568,13 +6570,13 @@
         <v>67</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M21" s="7"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="7" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B22" s="8">
         <v>46369</v>
@@ -6586,10 +6588,10 @@
         <v>68</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -6599,16 +6601,16 @@
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M22" s="7"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="7" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B23" s="8">
         <v>46397</v>
@@ -6620,10 +6622,10 @@
         <v>80</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -6633,16 +6635,16 @@
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="7" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B24" s="8">
         <v>46417</v>
@@ -6654,10 +6656,10 @@
         <v>90</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -6667,16 +6669,16 @@
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="7" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B25" s="8">
         <v>46425</v>
@@ -6688,10 +6690,10 @@
         <v>63</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -6701,16 +6703,16 @@
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M25" s="7"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B26" s="8">
         <v>46446</v>
@@ -6725,7 +6727,7 @@
         <v>223</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -6738,13 +6740,13 @@
         <v>84</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M26" s="7"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="7" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B27" s="8">
         <v>46452</v>
@@ -6759,7 +6761,7 @@
         <v>223</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -6772,13 +6774,13 @@
         <v>72</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M27" s="7"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B28" s="8">
         <v>46459</v>
@@ -6793,7 +6795,7 @@
         <v>223</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -6806,13 +6808,13 @@
         <v>110</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M28" s="7"/>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B29" s="8">
         <v>46467</v>
@@ -6827,7 +6829,7 @@
         <v>223</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
@@ -6840,7 +6842,7 @@
         <v>94</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M29" s="7"/>
     </row>
@@ -9957,7 +9959,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -9977,25 +9979,25 @@
         <v>111</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>116</v>
@@ -10013,7 +10015,7 @@
         <v>Sam Peters</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E4" s="7">
         <v>0</v>
@@ -19046,7 +19048,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -19070,25 +19072,25 @@
         <v>131</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>271</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>116</v>
@@ -23490,7 +23492,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -23504,34 +23506,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23539,7 +23541,7 @@
         <v>107</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -23551,16 +23553,16 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -23571,10 +23573,10 @@
         <v>86</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -23583,19 +23585,19 @@
         <v>0</v>
       </c>
       <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>32</v>
+      </c>
+      <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="G5">
+      <c r="J5">
         <v>12</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -23603,10 +23605,10 @@
         <v>75</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -23615,19 +23617,19 @@
         <v>1</v>
       </c>
       <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>23</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -23635,7 +23637,7 @@
         <v>48</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -23647,16 +23649,16 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -23667,31 +23669,31 @@
         <v>59</v>
       </c>
       <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -23699,10 +23701,10 @@
         <v>69</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -23711,19 +23713,19 @@
         <v>0</v>
       </c>
       <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>28</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>8</v>
-      </c>
       <c r="J9">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -23731,31 +23733,31 @@
         <v>53</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>43</v>
+      </c>
+      <c r="H10">
+        <v>20</v>
+      </c>
+      <c r="I10">
         <v>0</v>
       </c>
-      <c r="G10">
-        <v>27</v>
-      </c>
-      <c r="H10">
-        <v>9</v>
-      </c>
-      <c r="I10">
-        <v>18</v>
-      </c>
       <c r="J10">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -23763,31 +23765,31 @@
         <v>102</v>
       </c>
       <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11">
+        <v>26</v>
+      </c>
+      <c r="H11">
+        <v>33</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <v>8</v>
-      </c>
-      <c r="H11">
-        <v>17</v>
-      </c>
-      <c r="I11">
-        <v>9</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -23795,31 +23797,31 @@
         <v>31</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -23827,10 +23829,10 @@
         <v>81</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -23839,19 +23841,19 @@
         <v>0</v>
       </c>
       <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>21</v>
+      </c>
+      <c r="I13">
         <v>0</v>
       </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-      <c r="H13">
-        <v>2</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
       <c r="J13">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -23859,10 +23861,10 @@
         <v>64</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -23874,16 +23876,16 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H14">
+        <v>10</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
         <v>6</v>
-      </c>
-      <c r="I14">
-        <v>3</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -23891,10 +23893,10 @@
         <v>91</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -23903,19 +23905,19 @@
         <v>0</v>
       </c>
       <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <v>39</v>
+      </c>
+      <c r="H15">
+        <v>25</v>
+      </c>
+      <c r="I15">
         <v>0</v>
       </c>
-      <c r="G15">
-        <v>26</v>
-      </c>
-      <c r="H15">
-        <v>7</v>
-      </c>
-      <c r="I15">
-        <v>19</v>
-      </c>
       <c r="J15">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -23923,7 +23925,7 @@
         <v>96</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -23932,22 +23934,22 @@
         <v>0</v>
       </c>
       <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>7</v>
+      </c>
+      <c r="H16">
+        <v>17</v>
+      </c>
+      <c r="I16">
         <v>0</v>
       </c>
-      <c r="F16">
+      <c r="J16">
         <v>1</v>
-      </c>
-      <c r="G16">
-        <v>3</v>
-      </c>
-      <c r="H16">
-        <v>5</v>
-      </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23968,7 +23970,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -23982,34 +23984,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -24017,10 +24019,10 @@
         <v>86</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -24029,19 +24031,19 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -24049,7 +24051,7 @@
         <v>48</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -24061,13 +24063,13 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -24081,31 +24083,31 @@
         <v>53</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -24113,31 +24115,31 @@
         <v>102</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -24145,31 +24147,31 @@
         <v>31</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -24177,7 +24179,7 @@
         <v>96</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -24186,19 +24188,19 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
         <v>1</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -24233,7 +24235,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -24247,10 +24249,10 @@
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -24258,35 +24260,35 @@
         <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>223</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="K3" s="13"/>
       <c r="L3" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M3" s="12">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -24336,11 +24338,11 @@
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24386,11 +24388,11 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24436,11 +24438,11 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24486,7 +24488,7 @@
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M7" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="223" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2347A85-3F4B-47A6-A22E-C04992FEF68B}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBB437ED-3F63-4749-9266-2BE7772CC269}"/>
   <bookViews>
-    <workbookView xWindow="5685" yWindow="3525" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32865" yWindow="3420" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -23562,7 +23562,8 @@
         <v>39</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <f>G4-H4</f>
+        <v>-34</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -23594,7 +23595,8 @@
         <v>17</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <f t="shared" ref="I5:I16" si="0">G5-H5</f>
+        <v>15</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -23626,7 +23628,8 @@
         <v>23</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-5</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -23658,7 +23661,8 @@
         <v>26</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-21</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -23690,7 +23694,8 @@
         <v>23</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-3</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -23722,7 +23727,8 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="J9">
         <v>12</v>
@@ -23754,7 +23760,8 @@
         <v>20</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="J10">
         <v>14</v>
@@ -23786,7 +23793,8 @@
         <v>33</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-7</v>
       </c>
       <c r="J11">
         <v>8</v>
@@ -23818,7 +23826,8 @@
         <v>18</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>11</v>
@@ -23850,7 +23859,8 @@
         <v>21</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-1</v>
       </c>
       <c r="J13">
         <v>8</v>
@@ -23882,7 +23892,8 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>6</v>
@@ -23914,7 +23925,8 @@
         <v>25</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="J15">
         <v>12</v>
@@ -23946,7 +23958,8 @@
         <v>17</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-10</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -24040,7 +24053,8 @@
         <v>15</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <f>G4-H4</f>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>9</v>
@@ -24072,7 +24086,8 @@
         <v>16</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <f t="shared" ref="I5:I9" si="0">G5-H5</f>
+        <v>-14</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -24104,7 +24119,8 @@
         <v>18</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>11</v>
@@ -24136,7 +24152,8 @@
         <v>25</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-7</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -24168,7 +24185,8 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>10</v>
@@ -24200,7 +24218,8 @@
         <v>17</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>-10</v>
       </c>
       <c r="J9">
         <v>0</v>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBB437ED-3F63-4749-9266-2BE7772CC269}"/>
+  <xr:revisionPtr revIDLastSave="230" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{299BDDE4-0539-4779-83CB-B635AD76EEDB}"/>
   <bookViews>
-    <workbookView xWindow="32865" yWindow="3420" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -6253,11 +6253,15 @@
       <c r="F12" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="G12" s="7">
+        <v>6</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
       <c r="I12" s="10" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>W</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7" t="s">
@@ -24361,7 +24365,7 @@
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24461,7 +24465,7 @@
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="230" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{299BDDE4-0539-4779-83CB-B635AD76EEDB}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA6A3C85-4BCE-4493-B5A3-555C24B0160E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -6253,15 +6253,11 @@
       <c r="F12" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="G12" s="7">
-        <v>6</v>
-      </c>
-      <c r="H12" s="7">
-        <v>0</v>
-      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
       <c r="I12" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>W</v>
+        <v/>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7" t="s">
@@ -24365,7 +24361,7 @@
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24465,7 +24461,7 @@
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA6A3C85-4BCE-4493-B5A3-555C24B0160E}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E68AA62-609A-4938-86AD-BB3F557F1C44}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -6255,10 +6255,7 @@
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="I12" s="10"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7" t="s">
         <v>230</v>
@@ -10005,7 +10002,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>117</v>
@@ -10035,7 +10032,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>121</v>
@@ -10065,7 +10062,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>124</v>
@@ -10095,7 +10092,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="7" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>133</v>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E68AA62-609A-4938-86AD-BB3F557F1C44}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD07FD13-0A7F-48E5-8FAC-8D701DC6E958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -721,45 +721,57 @@
     <t>Pre-season</t>
   </si>
   <si>
+    <t>G002</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>OT</t>
+  </si>
+  <si>
+    <t>G003</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>League/Cup</t>
+  </si>
+  <si>
+    <t>Planet Ice Milton Keynes</t>
+  </si>
+  <si>
+    <t>G004</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>SO</t>
+  </si>
+  <si>
+    <t>G005</t>
+  </si>
+  <si>
+    <t>League</t>
+  </si>
+  <si>
+    <t>G006</t>
+  </si>
+  <si>
+    <t>G007</t>
+  </si>
+  <si>
+    <t>G008</t>
+  </si>
+  <si>
+    <t>G009</t>
+  </si>
+  <si>
     <t>Upcoming</t>
   </si>
   <si>
-    <t>G002</t>
-  </si>
-  <si>
-    <t>G003</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>League/Cup</t>
-  </si>
-  <si>
-    <t>Planet Ice Milton Keynes</t>
-  </si>
-  <si>
-    <t>G004</t>
-  </si>
-  <si>
-    <t>G005</t>
-  </si>
-  <si>
-    <t>League</t>
-  </si>
-  <si>
-    <t>G006</t>
-  </si>
-  <si>
-    <t>G007</t>
-  </si>
-  <si>
-    <t>G008</t>
-  </si>
-  <si>
-    <t>G009</t>
-  </si>
-  <si>
     <t>G010</t>
   </si>
   <si>
@@ -871,18 +883,12 @@
     <t>GP</t>
   </si>
   <si>
-    <t>W</t>
-  </si>
-  <si>
     <t>OTW</t>
   </si>
   <si>
     <t>OTL</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>GF</t>
   </si>
   <si>
@@ -932,12 +938,6 @@
   </si>
   <si>
     <t>Losses</t>
-  </si>
-  <si>
-    <t>OT</t>
-  </si>
-  <si>
-    <t>SO</t>
   </si>
 </sst>
 </file>
@@ -1090,14 +1090,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1439,7 +1439,7 @@
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
       <c r="G1" s="22"/>
-      <c r="H1" s="16"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="6" t="s">
@@ -4281,66 +4281,66 @@
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="17">
         <v>98</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="G31" s="18"/>
+      <c r="G31" s="17"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="18">
         <v>81</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="F32" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="G32" s="19"/>
+      <c r="G32" s="18"/>
       <c r="H32" s="13"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="16">
         <v>0</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
       <c r="H33" s="13"/>
     </row>
     <row r="34" spans="1:8">
@@ -5981,7 +5981,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B5" s="8">
         <v>46270</v>
@@ -6005,10 +6005,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>296</v>
+        <v>227</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>46</v>
@@ -6018,7 +6018,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B6" s="8">
         <v>46278</v>
@@ -6030,10 +6030,10 @@
         <v>47</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
@@ -6047,14 +6047,14 @@
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B7" s="8">
         <v>46284</v>
@@ -6069,7 +6069,7 @@
         <v>223</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G7" s="7">
         <v>4</v>
@@ -6078,10 +6078,10 @@
         <v>5</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>297</v>
+        <v>234</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>56</v>
@@ -6091,7 +6091,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="7" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B8" s="8">
         <v>46285</v>
@@ -6103,10 +6103,10 @@
         <v>58</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G8" s="7">
         <v>6</v>
@@ -6119,17 +6119,17 @@
         <v>L</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>296</v>
+        <v>227</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B9" s="8">
         <v>46291</v>
@@ -6144,7 +6144,7 @@
         <v>223</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G9" s="7">
         <v>1</v>
@@ -6165,7 +6165,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B10" s="8">
         <v>46292</v>
@@ -6177,10 +6177,10 @@
         <v>85</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G10" s="7">
         <v>5</v>
@@ -6189,18 +6189,18 @@
         <v>3</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="7" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B11" s="8">
         <v>46298</v>
@@ -6212,10 +6212,10 @@
         <v>101</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G11" s="7">
         <v>4</v>
@@ -6229,45 +6229,45 @@
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B12" s="8">
         <v>46306</v>
       </c>
       <c r="C12" s="9">
-        <v>0.83333333333333304</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>106</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="10"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="7" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B13" s="8">
         <v>46312</v>
@@ -6282,7 +6282,7 @@
         <v>223</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -6295,13 +6295,13 @@
         <v>105</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="7" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B14" s="8">
         <v>46320</v>
@@ -6313,10 +6313,10 @@
         <v>95</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -6326,16 +6326,16 @@
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="7" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B15" s="8">
         <v>46327</v>
@@ -6350,7 +6350,7 @@
         <v>223</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -6363,13 +6363,13 @@
         <v>51</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="7" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B16" s="8">
         <v>46334</v>
@@ -6381,10 +6381,10 @@
         <v>52</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -6394,16 +6394,16 @@
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B17" s="8">
         <v>46340</v>
@@ -6415,10 +6415,10 @@
         <v>74</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -6428,16 +6428,16 @@
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M17" s="7"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="7" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B18" s="8">
         <v>46341</v>
@@ -6452,7 +6452,7 @@
         <v>223</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -6465,13 +6465,13 @@
         <v>99</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M18" s="7"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B19" s="8">
         <v>46354</v>
@@ -6486,7 +6486,7 @@
         <v>223</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -6499,13 +6499,13 @@
         <v>89</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M19" s="7"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B20" s="8">
         <v>46355</v>
@@ -6520,7 +6520,7 @@
         <v>223</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -6533,13 +6533,13 @@
         <v>62</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B21" s="8">
         <v>46368</v>
@@ -6554,7 +6554,7 @@
         <v>223</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -6567,13 +6567,13 @@
         <v>67</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M21" s="7"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="7" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B22" s="8">
         <v>46369</v>
@@ -6585,10 +6585,10 @@
         <v>68</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -6598,16 +6598,16 @@
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M22" s="7"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B23" s="8">
         <v>46397</v>
@@ -6619,10 +6619,10 @@
         <v>80</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -6632,16 +6632,16 @@
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B24" s="8">
         <v>46417</v>
@@ -6653,10 +6653,10 @@
         <v>90</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -6666,16 +6666,16 @@
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B25" s="8">
         <v>46425</v>
@@ -6687,10 +6687,10 @@
         <v>63</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -6700,16 +6700,16 @@
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M25" s="7"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="7" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B26" s="8">
         <v>46446</v>
@@ -6724,7 +6724,7 @@
         <v>223</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -6737,13 +6737,13 @@
         <v>84</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M26" s="7"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="7" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B27" s="8">
         <v>46452</v>
@@ -6758,7 +6758,7 @@
         <v>223</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -6771,13 +6771,13 @@
         <v>72</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M27" s="7"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B28" s="8">
         <v>46459</v>
@@ -6792,7 +6792,7 @@
         <v>223</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -6805,13 +6805,13 @@
         <v>110</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M28" s="7"/>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="7" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B29" s="8">
         <v>46467</v>
@@ -6826,7 +6826,7 @@
         <v>223</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
@@ -6839,7 +6839,7 @@
         <v>94</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="M29" s="7"/>
     </row>
@@ -9956,7 +9956,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -9976,25 +9976,25 @@
         <v>111</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>116</v>
@@ -10002,7 +10002,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>117</v>
@@ -10012,7 +10012,7 @@
         <v>Sam Peters</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E4" s="7">
         <v>0</v>
@@ -10032,7 +10032,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>121</v>
@@ -10062,7 +10062,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>124</v>
@@ -10092,7 +10092,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>133</v>
@@ -19045,7 +19045,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -19069,25 +19069,25 @@
         <v>131</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>116</v>
@@ -19104,7 +19104,7 @@
         <f>IF(B4="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v>Aaron Burton</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="20">
         <v>1.6666666666666667</v>
       </c>
       <c r="E4" s="7">
@@ -23489,7 +23489,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -23503,34 +23503,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23980,7 +23980,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -23994,34 +23994,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -24251,7 +24251,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -24265,10 +24265,10 @@
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -24276,35 +24276,35 @@
         <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>223</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K3" s="13"/>
       <c r="L3" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M3" s="12">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -24354,7 +24354,7 @@
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
@@ -24404,7 +24404,7 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
@@ -24454,7 +24454,7 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
@@ -24504,7 +24504,7 @@
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M7" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
@@ -25461,43 +25461,43 @@
       <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="20" t="str">
+      <c r="A30" s="19" t="str">
         <f>IF(Players!A30="","",Players!A30)</f>
         <v>P027</v>
       </c>
-      <c r="B30" s="20" t="str">
+      <c r="B30" s="19" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Charles Coney</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="19">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>88</v>
       </c>
-      <c r="D30" s="20" t="str">
+      <c r="D30" s="19" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="19">
         <f>IF(A30="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A30,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="19">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="19">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="19">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="19">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD07FD13-0A7F-48E5-8FAC-8D701DC6E958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="248" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF4CA7E3-39C6-44B5-A9E4-130453CFD95A}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="297">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -673,9 +673,6 @@
     <t>Cass  McCormack</t>
   </si>
   <si>
-    <t>McCormack</t>
-  </si>
-  <si>
     <t>Game ID</t>
   </si>
   <si>
@@ -721,223 +718,223 @@
     <t>Pre-season</t>
   </si>
   <si>
+    <t>Upcoming</t>
+  </si>
+  <si>
     <t>G002</t>
   </si>
   <si>
+    <t>G003</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>League/Cup</t>
+  </si>
+  <si>
+    <t>Planet Ice Milton Keynes</t>
+  </si>
+  <si>
+    <t>G004</t>
+  </si>
+  <si>
+    <t>G005</t>
+  </si>
+  <si>
+    <t>League</t>
+  </si>
+  <si>
+    <t>G006</t>
+  </si>
+  <si>
+    <t>G007</t>
+  </si>
+  <si>
+    <t>G008</t>
+  </si>
+  <si>
+    <t>G009</t>
+  </si>
+  <si>
+    <t>G010</t>
+  </si>
+  <si>
+    <t>G011</t>
+  </si>
+  <si>
+    <t>G012</t>
+  </si>
+  <si>
+    <t>G013</t>
+  </si>
+  <si>
+    <t>G014</t>
+  </si>
+  <si>
+    <t>G015</t>
+  </si>
+  <si>
+    <t>G016</t>
+  </si>
+  <si>
+    <t>G017</t>
+  </si>
+  <si>
+    <t>G018</t>
+  </si>
+  <si>
+    <t>G019</t>
+  </si>
+  <si>
+    <t>G020</t>
+  </si>
+  <si>
+    <t>G021</t>
+  </si>
+  <si>
+    <t>G022</t>
+  </si>
+  <si>
+    <t>G023</t>
+  </si>
+  <si>
+    <t>G024</t>
+  </si>
+  <si>
+    <t>G025</t>
+  </si>
+  <si>
+    <t>G026</t>
+  </si>
+  <si>
+    <t>Player Game Stats – one row per player per game</t>
+  </si>
+  <si>
+    <t>Player Name</t>
+  </si>
+  <si>
+    <t>Dressed?</t>
+  </si>
+  <si>
+    <t>Goals</t>
+  </si>
+  <si>
+    <t>Assists</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>PIM</t>
+  </si>
+  <si>
+    <t>+/-</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Netminder Game Stats</t>
+  </si>
+  <si>
+    <t>Minutes</t>
+  </si>
+  <si>
+    <t>Shots Against</t>
+  </si>
+  <si>
+    <t>Goals Against</t>
+  </si>
+  <si>
+    <t>Saves</t>
+  </si>
+  <si>
+    <t>Save %</t>
+  </si>
+  <si>
+    <t>Shutout?</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>League Table</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>GP</t>
+  </si>
+  <si>
     <t>W</t>
   </si>
   <si>
+    <t>OTW</t>
+  </si>
+  <si>
+    <t>OTL</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>GF</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>Cup Table</t>
+  </si>
+  <si>
+    <t>MK Thunder Season Player Totals</t>
+  </si>
+  <si>
+    <t>Team KPIs</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Pos</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Games entered</t>
+  </si>
+  <si>
+    <t>Goals scored</t>
+  </si>
+  <si>
+    <t>Goals against</t>
+  </si>
+  <si>
+    <t>Wins</t>
+  </si>
+  <si>
+    <t>Losses</t>
+  </si>
+  <si>
     <t>OT</t>
   </si>
   <si>
-    <t>G003</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>League/Cup</t>
-  </si>
-  <si>
-    <t>Planet Ice Milton Keynes</t>
-  </si>
-  <si>
-    <t>G004</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>SO</t>
-  </si>
-  <si>
-    <t>G005</t>
-  </si>
-  <si>
-    <t>League</t>
-  </si>
-  <si>
-    <t>G006</t>
-  </si>
-  <si>
-    <t>G007</t>
-  </si>
-  <si>
-    <t>G008</t>
-  </si>
-  <si>
-    <t>G009</t>
-  </si>
-  <si>
-    <t>Upcoming</t>
-  </si>
-  <si>
-    <t>G010</t>
-  </si>
-  <si>
-    <t>G011</t>
-  </si>
-  <si>
-    <t>G012</t>
-  </si>
-  <si>
-    <t>G013</t>
-  </si>
-  <si>
-    <t>G014</t>
-  </si>
-  <si>
-    <t>G015</t>
-  </si>
-  <si>
-    <t>G016</t>
-  </si>
-  <si>
-    <t>G017</t>
-  </si>
-  <si>
-    <t>G018</t>
-  </si>
-  <si>
-    <t>G019</t>
-  </si>
-  <si>
-    <t>G020</t>
-  </si>
-  <si>
-    <t>G021</t>
-  </si>
-  <si>
-    <t>G022</t>
-  </si>
-  <si>
-    <t>G023</t>
-  </si>
-  <si>
-    <t>G024</t>
-  </si>
-  <si>
-    <t>G025</t>
-  </si>
-  <si>
-    <t>G026</t>
-  </si>
-  <si>
-    <t>Player Game Stats – one row per player per game</t>
-  </si>
-  <si>
-    <t>Player Name</t>
-  </si>
-  <si>
-    <t>Dressed?</t>
-  </si>
-  <si>
-    <t>Goals</t>
-  </si>
-  <si>
-    <t>Assists</t>
-  </si>
-  <si>
-    <t>Points</t>
-  </si>
-  <si>
-    <t>PIM</t>
-  </si>
-  <si>
-    <t>+/-</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Netminder Game Stats</t>
-  </si>
-  <si>
-    <t>Minutes</t>
-  </si>
-  <si>
-    <t>Shots Against</t>
-  </si>
-  <si>
-    <t>Goals Against</t>
-  </si>
-  <si>
-    <t>Saves</t>
-  </si>
-  <si>
-    <t>Save %</t>
-  </si>
-  <si>
-    <t>Shutout?</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>League Table</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>OTW</t>
-  </si>
-  <si>
-    <t>OTL</t>
-  </si>
-  <si>
-    <t>GF</t>
-  </si>
-  <si>
-    <t>GA</t>
-  </si>
-  <si>
-    <t>GD</t>
-  </si>
-  <si>
-    <t>PTS</t>
-  </si>
-  <si>
-    <t>Cup Table</t>
-  </si>
-  <si>
-    <t>MK Thunder Season Player Totals</t>
-  </si>
-  <si>
-    <t>Team KPIs</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Pos</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>Games entered</t>
-  </si>
-  <si>
-    <t>Goals scored</t>
-  </si>
-  <si>
-    <t>Goals against</t>
-  </si>
-  <si>
-    <t>Wins</t>
-  </si>
-  <si>
-    <t>Losses</t>
   </si>
 </sst>
 </file>
@@ -1090,14 +1087,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1439,7 +1436,7 @@
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
       <c r="G1" s="22"/>
-      <c r="H1" s="21"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="6" t="s">
@@ -4281,73 +4278,71 @@
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="18">
         <v>98</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F31" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="G31" s="17"/>
+      <c r="G31" s="18"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="C32" s="18">
+      <c r="C32" s="19">
         <v>81</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="G32" s="18"/>
+      <c r="G32" s="19"/>
       <c r="H32" s="13"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="17">
         <v>0</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
       <c r="H33" s="13"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2"/>
-      <c r="B34" s="2" t="s">
-        <v>209</v>
-      </c>
+      <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -5904,40 +5899,40 @@
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
       <c r="A3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="M3" s="6" t="s">
         <v>116</v>
@@ -5945,7 +5940,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B4" s="8">
         <v>46264</v>
@@ -5957,10 +5952,10 @@
         <v>37</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>224</v>
       </c>
       <c r="G4" s="7">
         <v>12</v>
@@ -5993,10 +5988,10 @@
         <v>42</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>224</v>
       </c>
       <c r="G5" s="7">
         <v>5</v>
@@ -6005,10 +6000,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>46</v>
@@ -6018,7 +6013,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B6" s="8">
         <v>46278</v>
@@ -6030,10 +6025,10 @@
         <v>47</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
@@ -6047,14 +6042,14 @@
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B7" s="8">
         <v>46284</v>
@@ -6066,10 +6061,10 @@
         <v>52</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G7" s="7">
         <v>4</v>
@@ -6078,10 +6073,10 @@
         <v>5</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>233</v>
+        <v>277</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>56</v>
@@ -6091,7 +6086,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B8" s="8">
         <v>46285</v>
@@ -6103,10 +6098,10 @@
         <v>58</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G8" s="7">
         <v>6</v>
@@ -6119,17 +6114,17 @@
         <v>L</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B9" s="8">
         <v>46291</v>
@@ -6141,10 +6136,10 @@
         <v>74</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G9" s="7">
         <v>1</v>
@@ -6165,7 +6160,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="7" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B10" s="8">
         <v>46292</v>
@@ -6177,10 +6172,10 @@
         <v>85</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G10" s="7">
         <v>5</v>
@@ -6189,18 +6184,18 @@
         <v>3</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B11" s="8">
         <v>46298</v>
@@ -6212,10 +6207,10 @@
         <v>101</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G11" s="7">
         <v>4</v>
@@ -6229,14 +6224,14 @@
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B12" s="8">
         <v>46306</v>
@@ -6248,26 +6243,26 @@
         <v>106</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="10"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="7" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B13" s="8">
         <v>46312</v>
@@ -6279,10 +6274,10 @@
         <v>101</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -6295,13 +6290,13 @@
         <v>105</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="7" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B14" s="8">
         <v>46320</v>
@@ -6313,10 +6308,10 @@
         <v>95</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -6326,16 +6321,16 @@
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B15" s="8">
         <v>46327</v>
@@ -6347,10 +6342,10 @@
         <v>47</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -6363,13 +6358,13 @@
         <v>51</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B16" s="8">
         <v>46334</v>
@@ -6381,10 +6376,10 @@
         <v>52</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -6394,16 +6389,16 @@
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="7" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B17" s="8">
         <v>46340</v>
@@ -6415,10 +6410,10 @@
         <v>74</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -6428,16 +6423,16 @@
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M17" s="7"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="7" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B18" s="8">
         <v>46341</v>
@@ -6449,10 +6444,10 @@
         <v>95</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -6465,13 +6460,13 @@
         <v>99</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M18" s="7"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B19" s="8">
         <v>46354</v>
@@ -6483,10 +6478,10 @@
         <v>85</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -6499,13 +6494,13 @@
         <v>89</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M19" s="7"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="7" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B20" s="8">
         <v>46355</v>
@@ -6517,10 +6512,10 @@
         <v>58</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -6533,13 +6528,13 @@
         <v>62</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="7" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B21" s="8">
         <v>46368</v>
@@ -6551,10 +6546,10 @@
         <v>63</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -6567,13 +6562,13 @@
         <v>67</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M21" s="7"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="7" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B22" s="8">
         <v>46369</v>
@@ -6585,10 +6580,10 @@
         <v>68</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -6598,16 +6593,16 @@
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M22" s="7"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B23" s="8">
         <v>46397</v>
@@ -6619,10 +6614,10 @@
         <v>80</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -6632,16 +6627,16 @@
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="7" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B24" s="8">
         <v>46417</v>
@@ -6653,10 +6648,10 @@
         <v>90</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -6666,16 +6661,16 @@
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="7" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B25" s="8">
         <v>46425</v>
@@ -6687,10 +6682,10 @@
         <v>63</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -6700,16 +6695,16 @@
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M25" s="7"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="7" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B26" s="8">
         <v>46446</v>
@@ -6721,10 +6716,10 @@
         <v>80</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -6737,13 +6732,13 @@
         <v>84</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M26" s="7"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="7" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B27" s="8">
         <v>46452</v>
@@ -6755,10 +6750,10 @@
         <v>68</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -6771,13 +6766,13 @@
         <v>72</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M27" s="7"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B28" s="8">
         <v>46459</v>
@@ -6789,10 +6784,10 @@
         <v>106</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -6805,13 +6800,13 @@
         <v>110</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M28" s="7"/>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="7" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B29" s="8">
         <v>46467</v>
@@ -6823,10 +6818,10 @@
         <v>90</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
@@ -6839,7 +6834,7 @@
         <v>94</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M29" s="7"/>
     </row>
@@ -9956,7 +9951,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -9970,31 +9965,31 @@
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>116</v>
@@ -10002,7 +9997,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>117</v>
@@ -10012,7 +10007,7 @@
         <v>Sam Peters</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E4" s="7">
         <v>0</v>
@@ -10032,7 +10027,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>121</v>
@@ -10062,7 +10057,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>124</v>
@@ -10092,7 +10087,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>133</v>
@@ -10121,20 +10116,32 @@
       <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>136</v>
+      </c>
       <c r="C8" s="10" t="str">
         <f>IF(B8="","",IFERROR(VLOOKUP(B8,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="10" t="str">
+        <v>Lewis Smith</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3</v>
+      </c>
+      <c r="F8" s="7">
+        <v>4</v>
+      </c>
+      <c r="G8" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H8" s="7"/>
+        <v>7</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
     </row>
@@ -19045,7 +19052,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -19060,7 +19067,7 @@
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>111</v>
@@ -19069,25 +19076,25 @@
         <v>131</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>270</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>116</v>
@@ -19095,7 +19102,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>129</v>
@@ -19104,7 +19111,7 @@
         <f>IF(B4="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v>Aaron Burton</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="21">
         <v>1.6666666666666667</v>
       </c>
       <c r="E4" s="7">
@@ -23489,7 +23496,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -23503,34 +23510,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23980,7 +23987,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -23994,34 +24001,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -24251,7 +24258,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -24265,10 +24272,10 @@
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -24276,35 +24283,35 @@
         <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="K3" s="13"/>
       <c r="L3" s="12" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="M3" s="12">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -24329,20 +24336,17 @@
         <v>Forward</v>
       </c>
       <c r="E4" s="12">
-        <f>IF(A4="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A4,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="12">
-        <f>IF(A4="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4" s="12">
-        <f>IF(A4="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" ref="H4:H35" si="0">IF(A4="","",F4+G4)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I4" s="12">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
@@ -24354,7 +24358,7 @@
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="12" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
@@ -24404,7 +24408,7 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="12" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
@@ -24454,7 +24458,7 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="12" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
@@ -24504,7 +24508,7 @@
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="12" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="M7" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>
@@ -24575,19 +24579,19 @@
       </c>
       <c r="E9" s="15">
         <f>IF(A9="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A9,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="15">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" s="15">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9" s="15">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
@@ -25461,43 +25465,43 @@
       <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="19" t="str">
+      <c r="A30" s="20" t="str">
         <f>IF(Players!A30="","",Players!A30)</f>
         <v>P027</v>
       </c>
-      <c r="B30" s="19" t="str">
+      <c r="B30" s="20" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Charles Coney</v>
       </c>
-      <c r="C30" s="19">
+      <c r="C30" s="20">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>88</v>
       </c>
-      <c r="D30" s="19" t="str">
+      <c r="D30" s="20" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="20">
         <f>IF(A30="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A30,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F30" s="20">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="20">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="20">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="J30" s="19">
+      <c r="J30" s="20">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/Files/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="248" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF4CA7E3-39C6-44B5-A9E4-130453CFD95A}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D41309F-E73D-4DD8-BCA4-B74A9F68829D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2895" yWindow="3240" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -6248,16 +6248,20 @@
       <c r="F12" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="10"/>
+      <c r="G12" s="7">
+        <v>7</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>274</v>
+      </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="L12" s="7" t="s">
-        <v>224</v>
-      </c>
+      <c r="L12" s="7"/>
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:13">
@@ -23545,7 +23549,7 @@
         <v>107</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -23557,17 +23561,17 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
       <c r="H4">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I4">
         <f>G4-H4</f>
-        <v>-34</v>
+        <v>-41</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -23578,7 +23582,7 @@
         <v>86</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -23590,17 +23594,17 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H5">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I5">
         <f t="shared" ref="I5:I16" si="0">G5-H5</f>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -23677,10 +23681,10 @@
         <v>59</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -23692,17 +23696,17 @@
         <v>2</v>
       </c>
       <c r="G8">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -23710,7 +23714,7 @@
         <v>69</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -23722,17 +23726,17 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J9">
         <v>12</v>
@@ -23743,10 +23747,10 @@
         <v>53</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -23758,17 +23762,17 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J10">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -23776,7 +23780,7 @@
         <v>102</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -23788,17 +23792,17 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="J11">
         <v>8</v>
@@ -23809,10 +23813,10 @@
         <v>31</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -23824,17 +23828,17 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H12">
         <v>18</v>
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J12">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -23908,7 +23912,7 @@
         <v>91</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -23920,17 +23924,17 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I15">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J15">
         <v>12</v>
@@ -24036,10 +24040,10 @@
         <v>86</v>
       </c>
       <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
         <v>4</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -24051,17 +24055,17 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4">
         <f>G4-H4</f>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -24135,7 +24139,7 @@
         <v>102</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -24147,17 +24151,17 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -24362,7 +24366,7 @@
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24462,7 +24466,7 @@
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/Files/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D41309F-E73D-4DD8-BCA4-B74A9F68829D}"/>
+  <xr:revisionPtr revIDLastSave="297" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DAC9839-42B3-4601-9EFE-44D5CA29EA27}"/>
   <bookViews>
-    <workbookView xWindow="2895" yWindow="3240" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -24340,17 +24340,17 @@
         <v>Forward</v>
       </c>
       <c r="E4" s="12">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F4" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" ref="H4:H35" si="0">IF(A4="","",F4+G4)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I4" s="12">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A4))</f>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/Files/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="297" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DAC9839-42B3-4601-9EFE-44D5CA29EA27}"/>
+  <xr:revisionPtr revIDLastSave="299" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC6E6AFF-E756-447B-86B2-8A6EAC440F52}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -10014,14 +10014,14 @@
         <v>262</v>
       </c>
       <c r="E4" s="7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4" s="7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G4" s="10">
         <f>IF(AND(E4="",E4=""),"",SUM(E4:F4))</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H4" s="7">
         <v>0</v>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/Files/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="299" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC6E6AFF-E756-447B-86B2-8A6EAC440F52}"/>
+  <xr:revisionPtr revIDLastSave="300" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B27F902-F45C-4895-9C96-6AE26E6C7B0C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="296">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -830,9 +830,6 @@
   </si>
   <si>
     <t>+/-</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>Netminder Game Stats</t>
@@ -6000,10 +5997,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>46</v>
@@ -6073,10 +6070,10 @@
         <v>5</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>56</v>
@@ -6114,7 +6111,7 @@
         <v>L</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>229</v>
@@ -6184,7 +6181,7 @@
         <v>3</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7" t="s">
@@ -6255,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7" t="s">
@@ -10011,7 +10008,7 @@
         <v>Sam Peters</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>262</v>
+        <v>36</v>
       </c>
       <c r="E4" s="7">
         <v>7</v>
@@ -19056,7 +19053,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -19080,25 +19077,25 @@
         <v>131</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>116</v>
@@ -23500,7 +23497,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -23514,34 +23511,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23991,7 +23988,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -24005,34 +24002,34 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -24262,7 +24259,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
       <c r="A1" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -24276,10 +24273,10 @@
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="M2" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -24287,25 +24284,25 @@
         <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>222</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>260</v>
@@ -24315,7 +24312,7 @@
       </c>
       <c r="K3" s="13"/>
       <c r="L3" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M3" s="12">
         <f>COUNT(Games!$A$4:$A$200)</f>
@@ -24362,7 +24359,7 @@
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M4" s="12">
         <f>SUM(Games!$G$4:$G$200)</f>
@@ -24412,7 +24409,7 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M5" s="12">
         <f>SUM(Games!$H$4:$H$200)</f>
@@ -24462,7 +24459,7 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M6" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"W")</f>
@@ -24512,7 +24509,7 @@
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M7" s="12">
         <f>COUNTIF(Games!$I$4:$I$200,"L")</f>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/Files/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="300" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B27F902-F45C-4895-9C96-6AE26E6C7B0C}"/>
+  <xr:revisionPtr revIDLastSave="444" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8F13CA7-6673-449B-BB42-87608FC141A8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="296">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -10001,24 +10001,23 @@
         <v>226</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="C4" s="10" t="str">
         <f>IF(B5="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v>Sam Peters</v>
+        <v>Cass  McCormack</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E4" s="7">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4" s="7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G4" s="10">
-        <f>IF(AND(E4="",E4=""),"",SUM(E4:F4))</f>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H4" s="7">
         <v>0</v>
@@ -10031,11 +10030,11 @@
         <v>226</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C5" s="10" t="str">
         <f>IF(B5="","",IFERROR(VLOOKUP(B5,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v>Marks Kanins</v>
+        <v>Charlie Russell</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>36</v>
@@ -10044,14 +10043,14 @@
         <v>1</v>
       </c>
       <c r="F5" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="10">
         <f>IF(AND(E5="",F5=""),"",SUM(E5:F5))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
@@ -10061,11 +10060,11 @@
         <v>226</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C6" s="10" t="str">
         <f>IF(B6="","",IFERROR(VLOOKUP(B6,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v>Dominic Wealthall</v>
+        <v>Lewis Smith</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>36</v>
@@ -10074,11 +10073,11 @@
         <v>0</v>
       </c>
       <c r="F6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10">
         <f t="shared" ref="G6:G67" si="0">IF(AND(E6="",F6=""),"",SUM(E6:F6))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="7">
         <v>7</v>
@@ -10091,27 +10090,27 @@
         <v>226</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C7" s="10" t="str">
         <f>IF(B7="","",IFERROR(VLOOKUP(B7,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v>Charlie Russell</v>
+        <v>Joshua Blackwood</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E7" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -10121,24 +10120,24 @@
         <v>226</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="C8" s="10" t="str">
         <f>IF(B8="","",IFERROR(VLOOKUP(B8,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v>Lewis Smith</v>
+        <v>Harry MacGarvery</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E8" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="10">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H8" s="7">
         <v>0</v>
@@ -10147,92 +10146,152 @@
       <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>160</v>
+      </c>
       <c r="C9" s="10" t="str">
         <f>IF(B9="","",IFERROR(VLOOKUP(B9,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="10" t="str">
+        <v>Chalie Conroy</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H9" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>168</v>
+      </c>
       <c r="C10" s="10" t="str">
         <f>IF(B10="","",IFERROR(VLOOKUP(B10,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="10" t="str">
+        <v>Hayden Hagger</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7">
+        <v>2</v>
+      </c>
+      <c r="G10" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H10" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>124</v>
+      </c>
       <c r="C11" s="10" t="str">
         <f>IF(B11="","",IFERROR(VLOOKUP(B11,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="10" t="str">
+        <v>Dominic Wealthall</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H11" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="H11" s="7">
+        <v>7</v>
+      </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>195</v>
+      </c>
       <c r="C12" s="10" t="str">
         <f>IF(B12="","",IFERROR(VLOOKUP(B12,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="10" t="str">
+        <v>Ryan Wonfor</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1</v>
+      </c>
+      <c r="G12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H12" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>201</v>
+      </c>
       <c r="C13" s="10" t="str">
         <f>IF(B13="","",IFERROR(VLOOKUP(B13,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="10" t="str">
+        <v>Will Nowik</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2</v>
+      </c>
+      <c r="F13" s="7">
+        <v>2</v>
+      </c>
+      <c r="G13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H13" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="H13" s="7">
+        <v>2</v>
+      </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
     </row>
@@ -24337,17 +24396,20 @@
         <v>Forward</v>
       </c>
       <c r="E4" s="12">
-        <v>7</v>
+        <f>IF(A4="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A4,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
+        <v>0</v>
       </c>
       <c r="F4" s="12">
-        <v>7</v>
+        <f>IF(A4="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
+        <v>0</v>
       </c>
       <c r="G4" s="12">
-        <v>7</v>
+        <f>IF(A4="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
+        <v>0</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" ref="H4:H35" si="0">IF(A4="","",F4+G4)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I4" s="12">
         <f>IF(A4="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A4))</f>
@@ -24385,19 +24447,19 @@
       </c>
       <c r="E5" s="12">
         <f>IF(A5="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A5,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="12">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="12">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" s="12">
         <f>IF(A5="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A5))</f>
@@ -24539,19 +24601,19 @@
       </c>
       <c r="F8" s="12">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="12">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I8" s="12">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J8" s="12">
         <f>IF(A8="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A8))</f>
@@ -24584,19 +24646,19 @@
       </c>
       <c r="F9" s="15">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="15">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H9" s="15">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I9" s="15">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J9" s="15">
         <f>IF(A9="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A9))</f>
@@ -24839,7 +24901,7 @@
       </c>
       <c r="E15" s="14">
         <f>IF(A15="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A15,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="14">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
@@ -24855,7 +24917,7 @@
       </c>
       <c r="I15" s="14">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="14">
         <f>IF(A15="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A15))</f>
@@ -24882,7 +24944,7 @@
       </c>
       <c r="E16" s="14">
         <f>IF(A16="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A16,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="14">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
@@ -24890,11 +24952,11 @@
       </c>
       <c r="G16" s="14">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" s="14">
         <f>IF(A16="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A16))</f>
@@ -24925,7 +24987,7 @@
       </c>
       <c r="E17" s="14">
         <f>IF(A17="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A17,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="14">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
@@ -24933,11 +24995,11 @@
       </c>
       <c r="G17" s="14">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="14">
         <f>IF(A17="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A17))</f>
@@ -25054,7 +25116,7 @@
       </c>
       <c r="E20" s="14">
         <f>IF(A20="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A20,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="14">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
@@ -25062,11 +25124,11 @@
       </c>
       <c r="G20" s="14">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="14">
         <f>IF(A20="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A20))</f>
@@ -25441,19 +25503,19 @@
       </c>
       <c r="E29" s="14">
         <f>IF(A29="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A29,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="14">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="14">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
@@ -25527,23 +25589,23 @@
       </c>
       <c r="E31" s="14">
         <f>IF(A31="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A31,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
@@ -25613,11 +25675,11 @@
       </c>
       <c r="E33" s="14">
         <f>IF(A33="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A33,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="14">
         <f>IF(A33="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A33))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="14">
         <f>IF(A33="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A33))</f>
@@ -25625,7 +25687,7 @@
       </c>
       <c r="H33" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="14">
         <f>IF(A33="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A33))</f>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/Files/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="444" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8F13CA7-6673-449B-BB42-87608FC141A8}"/>
+  <xr:revisionPtr revIDLastSave="450" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8096D068-DFE5-42BD-B911-D03FAAFCB2D4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30645" yWindow="1035" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="296">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -10296,20 +10296,32 @@
       <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>201</v>
+      </c>
       <c r="C14" s="10" t="str">
         <f>IF(B14="","",IFERROR(VLOOKUP(B14,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="10" t="str">
+        <v>Will Nowik</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7">
+        <v>1</v>
+      </c>
+      <c r="G14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H14" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0</v>
+      </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
     </row>
@@ -25589,19 +25601,19 @@
       </c>
       <c r="E31" s="14">
         <f>IF(A31="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A31,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A31))</f>

--- a/MK_Thunder_Stats_Master.xlsx
+++ b/MK_Thunder_Stats_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/mark_ward_rockwellautomation_com/Documents/Desktop/Files/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="450" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8096D068-DFE5-42BD-B911-D03FAAFCB2D4}"/>
+  <xr:revisionPtr revIDLastSave="477" documentId="13_ncr:1_{3A096520-12A4-43F2-9693-BC14297102B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC23B355-2F55-4F15-9534-F154E75C8B2D}"/>
   <bookViews>
-    <workbookView xWindow="30645" yWindow="1035" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="298">
   <si>
     <t>MK Thunder Stats – Excel Control Workbook</t>
   </si>
@@ -932,6 +932,12 @@
   </si>
   <si>
     <t>SO</t>
+  </si>
+  <si>
+    <t>P031</t>
+  </si>
+  <si>
+    <t>George Gell</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1069,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1087,7 +1093,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -1316,14 +1321,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="30">
       <c r="A3" s="1" t="s">
@@ -1424,15 +1429,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
       <c r="H1" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="15">
@@ -3674,15 +3679,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
     </row>
     <row r="3" spans="1:7" ht="30">
       <c r="A3" s="6" t="s">
@@ -4275,76 +4280,86 @@
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="17">
         <v>98</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="G31" s="18"/>
+      <c r="G31" s="17"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="18">
         <v>81</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="F32" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="G32" s="19"/>
+      <c r="G32" s="18"/>
       <c r="H32" s="13"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="18">
         <v>0</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
       <c r="H33" s="13"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
+      <c r="A34" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C34" s="7">
+        <v>7</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2"/>
@@ -5877,21 +5892,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
     </row>
     <row r="2" spans="1:13"/>
     <row r="3" spans="1:13" ht="30">
@@ -9951,18 +9966,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="6" t="s">
@@ -10300,24 +10315,24 @@
         <v>230</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>201</v>
+        <v>296</v>
       </c>
       <c r="C14" s="10" t="str">
         <f>IF(B14="","",IFERROR(VLOOKUP(B14,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v>Will Nowik</v>
+        <v>George Gell</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E14" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" s="10">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="7">
         <v>0</v>
@@ -10326,56 +10341,92 @@
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>195</v>
+      </c>
       <c r="C15" s="10" t="str">
         <f>IF(B15="","",IFERROR(VLOOKUP(B15,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="10" t="str">
+        <v>Ryan Wonfor</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7">
+        <v>3</v>
+      </c>
+      <c r="G15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H15" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0</v>
+      </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>201</v>
+      </c>
       <c r="C16" s="10" t="str">
         <f>IF(B16="","",IFERROR(VLOOKUP(B16,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="10" t="str">
+        <v>Will Nowik</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="7">
+        <v>4</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H16" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0</v>
+      </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
+      <c r="A17" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>296</v>
+      </c>
       <c r="C17" s="10" t="str">
         <f>IF(B17="","",IFERROR(VLOOKUP(B17,Players!$A$4:$B$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="10" t="str">
+        <v>George Gell</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7">
+        <v>2</v>
+      </c>
+      <c r="G17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H17" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="H17" s="7">
+        <v>43</v>
+      </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
     </row>
@@ -19123,19 +19174,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="6" t="s">
@@ -19183,7 +19234,7 @@
         <f>IF(B4="","",IFERROR(VLOOKUP(B4,Players!$A$4:$B$200,2,FALSE),""))</f>
         <v>Aaron Burton</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="20">
         <v>1.6666666666666667</v>
       </c>
       <c r="E4" s="7">
@@ -23567,18 +23618,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
@@ -24058,18 +24109,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="6" t="s">
@@ -24329,18 +24380,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
     </row>
     <row r="2" spans="1:13" ht="15">
       <c r="L2" s="6" t="s">
@@ -25515,7 +25566,7 @@
       </c>
       <c r="E29" s="14">
         <f>IF(A29="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A29,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="14">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
@@ -25523,11 +25574,11 @@
       </c>
       <c r="G29" s="14">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29" s="14">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I29" s="14">
         <f>IF(A29="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A29))</f>
@@ -25540,43 +25591,43 @@
       <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="20" t="str">
+      <c r="A30" s="19" t="str">
         <f>IF(Players!A30="","",Players!A30)</f>
         <v>P027</v>
       </c>
-      <c r="B30" s="20" t="str">
+      <c r="B30" s="19" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,2,FALSE),""))</f>
         <v>Charles Coney</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="19">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,3,FALSE),""))</f>
         <v>88</v>
       </c>
-      <c r="D30" s="20" t="str">
+      <c r="D30" s="19" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Players!$A$4:$D$200,4,FALSE),""))</f>
         <v>Defence</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="19">
         <f>IF(A30="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A30,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
         <v>0</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="19">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="19">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="19">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="19">
         <f>IF(A30="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A30))</f>
         <v>0</v>
       </c>
@@ -25605,15 +25656,15 @@
       </c>
       <c r="F31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I31" s="14">
         <f>IF(A31="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A31))</f>
@@ -25714,43 +25765,43 @@
     <row r="34" spans="1:11">
       <c r="A34" s="13" t="str">
         <f>IF(Players!A34="","",Players!A34)</f>
-        <v/>
+        <v>P031</v>
       </c>
       <c r="B34" s="13" t="str">
         <f>IF(A34="","",IFERROR(VLOOKUP(A34,Players!$A$4:$D$200,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="C34" s="13" t="str">
+        <v>George Gell</v>
+      </c>
+      <c r="C34" s="13">
         <f>IF(A34="","",IFERROR(VLOOKUP(A34,Players!$A$4:$D$200,3,FALSE),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="D34" s="13" t="str">
         <f>IF(A34="","",IFERROR(VLOOKUP(A34,Players!$A$4:$D$200,4,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="E34" s="13" t="str">
+        <v>Forward</v>
+      </c>
+      <c r="E34" s="13">
         <f>IF(A34="","",COUNTIFS('Player Game Stats'!$B$4:$B$500,A34,'Player Game Stats'!$D$4:$D$500,"Yes"))</f>
-        <v/>
-      </c>
-      <c r="F34" s="13" t="str">
+        <v>2</v>
+      </c>
+      <c r="F34" s="13">
         <f>IF(A34="","",SUMIFS('Player Game Stats'!$E$4:$E$500,'Player Game Stats'!$B$4:$B$500,A34))</f>
-        <v/>
-      </c>
-      <c r="G34" s="13" t="str">
+        <v>0</v>
+      </c>
+      <c r="G34" s="13">
         <f>IF(A34="","",SUMIFS('Player Game Stats'!$F$4:$F$500,'Player Game Stats'!$B$4:$B$500,A34))</f>
-        <v/>
-      </c>
-      <c r="H34" s="13" t="str">
+        <v>5</v>
+      </c>
+      <c r="H34" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I34" s="13" t="str">
+        <v>5</v>
+      </c>
+      <c r="I34" s="13">
         <f>IF(A34="","",SUMIFS('Player Game Stats'!$H$4:$H$500,'Player Game Stats'!$B$4:$B$500,A34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="13" t="str">
+        <v>43</v>
+      </c>
+      <c r="J34" s="13">
         <f>IF(A34="","",SUMIFS('Player Game Stats'!$I$4:$I$500,'Player Game Stats'!$B$4:$B$500,A34))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
